--- a/evidencias/quinto_avance/Lista_Chequeo_Quinto_Avance_DILIGENCIADA.xlsx
+++ b/evidencias/quinto_avance/Lista_Chequeo_Quinto_Avance_DILIGENCIADA.xlsx
@@ -952,7 +952,7 @@
       <row>18</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5191125" cy="4143375"/>
+    <ext cx="5191125" cy="3762375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -1452,7 +1452,7 @@
       <row>38</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5191125" cy="3533775"/>
+    <ext cx="5191125" cy="4105275"/>
     <pic>
       <nvPicPr>
         <cNvPr id="26" name="Image 26" descr="Picture"/>
@@ -1919,7 +1919,7 @@
       <c r="E7" s="45" t="n"/>
       <c r="F7" s="34" t="inlineStr">
         <is>
-          <t xml:space="preserve">03 / Ambiente </t>
+          <t>03 / Ambiente 702</t>
         </is>
       </c>
       <c r="G7" s="45" t="n"/>
@@ -2115,11 +2115,7 @@
           <t>Cumplido</t>
         </is>
       </c>
-      <c r="F15" s="19" t="inlineStr">
-        <is>
-          <t>[Pegar Captura de Pantalla Aquí]</t>
-        </is>
-      </c>
+      <c r="F15" s="19" t="n"/>
       <c r="G15" s="46" t="inlineStr">
         <is>
           <t>POST /api/ventas registra la venta con cliente, vendedor, productos, servicios, cantidades, descuentos, subtotal, IVA del 19%, total, forma de pago, fecha y estado. Los precios se leen del catalogo, nunca de la peticion. Descuenta inventario y anular lo devuelve. Se puede registrar desde el panel o desde el carrito del sitio.</t>
@@ -2152,11 +2148,7 @@
           <t>Cumplido</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
-        <is>
-          <t>[Pegar Captura de Pantalla Aquí]</t>
-        </is>
-      </c>
+      <c r="F16" s="19" t="n"/>
       <c r="G16" s="47" t="inlineStr">
         <is>
           <t>Tabla detalle_ventas: una fila por articulo con tipo (producto o servicio), cantidad, precio unitario, descuento y subtotal. Guarda copia del nombre y del precio del momento, asi el historico no cambia si el articulo se edita o se retira del catalogo.</t>
@@ -2189,11 +2181,7 @@
           <t>Cumplido</t>
         </is>
       </c>
-      <c r="F17" s="19" t="inlineStr">
-        <is>
-          <t>[Pegar Captura de Pantalla Aquí]</t>
-        </is>
-      </c>
+      <c r="F17" s="19" t="n"/>
       <c r="G17" s="46" t="inlineStr">
         <is>
           <t>GET /api/ventas filtra por fecha inicial y final, cliente, producto, servicio, estado, forma de pago, valor minimo y maximo, y texto libre sobre numero de venta, nombre, correo o documento. El cliente solo recibe sus propias compras.</t>
@@ -2226,18 +2214,14 @@
           <t>Cumplido</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
-        <is>
-          <t>[Pegar Captura de Pantalla Aquí]</t>
-        </is>
-      </c>
+      <c r="F18" s="19" t="n"/>
       <c r="G18" s="47" t="inlineStr">
         <is>
           <t>GET /api/reportes/ventas-diarias devuelve fecha, numero de venta, cliente, productos y servicios, cantidad, valor, total y estado. Los tres formatos (pantalla, PDF y Excel) salen de un unico calculo, para que no puedan discrepar entre si.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="330.6" customHeight="1" s="43">
+    <row r="19" ht="300.2" customHeight="1" s="43">
       <c r="A19" s="24" t="inlineStr">
         <is>
           <t>REQ-05</t>
@@ -2263,11 +2247,7 @@
           <t>Cumplido</t>
         </is>
       </c>
-      <c r="F19" s="19" t="inlineStr">
-        <is>
-          <t>[Pegar Captura de Pantalla Aquí]</t>
-        </is>
-      </c>
+      <c r="F19" s="19" t="n"/>
       <c r="G19" s="46" t="inlineStr">
         <is>
           <t>Generado con ReportLab. Incluye nombre y NIT del negocio, fecha del reporte, tabla de ventas, totales con IVA y sello de generacion. Se pagina solo si el dia tiene muchas ventas. Las anuladas aparecen listadas pero no suman al total.</t>
@@ -2300,11 +2280,7 @@
           <t>Cumplido</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
-        <is>
-          <t>[Pegar Captura de Pantalla Aquí]</t>
-        </is>
-      </c>
+      <c r="F20" s="19" t="n"/>
       <c r="G20" s="47" t="inlineStr">
         <is>
           <t>Generado con openpyxl. Tres hojas: Ventas, Detalle (una fila por articulo, para analizar) y Resumen. Trae autofiltro, primera fila congelada, formato de moneda y formulas =SUM() vivas, de modo que al filtrar los totales se recalculan solos.</t>
@@ -2337,11 +2313,7 @@
           <t>Cumplido</t>
         </is>
       </c>
-      <c r="F21" s="19" t="inlineStr">
-        <is>
-          <t>[Pegar Captura de Pantalla Aquí]</t>
-        </is>
-      </c>
+      <c r="F21" s="19" t="n"/>
       <c r="G21" s="46" t="inlineStr">
         <is>
           <t>La factura nace de una venta registrada y lleva numero consecutivo (FV-2026-000061), fecha, datos del cliente, detalle con cantidad y precio unitario, subtotal, IVA y total. Copia los datos del cliente al emitirse: es un documento y no cambia despues.</t>
@@ -2374,11 +2346,7 @@
           <t>Cumplido</t>
         </is>
       </c>
-      <c r="F22" s="19" t="inlineStr">
-        <is>
-          <t>[Pegar Captura de Pantalla Aquí]</t>
-        </is>
-      </c>
+      <c r="F22" s="19" t="n"/>
       <c r="G22" s="47" t="inlineStr">
         <is>
           <t>GET /api/facturas busca por numero de factura, nombre, documento o correo del cliente, rango de fechas y estado. El cliente ve unicamente las suyas, y el recorte lo hace FastAPI a partir del rol del token.</t>
@@ -2411,11 +2379,7 @@
           <t>Cumplido</t>
         </is>
       </c>
-      <c r="F23" s="19" t="inlineStr">
-        <is>
-          <t>[Pegar Captura de Pantalla Aquí]</t>
-        </is>
-      </c>
+      <c r="F23" s="19" t="n"/>
       <c r="G23" s="46" t="inlineStr">
         <is>
           <t>GET /api/facturas/{id}/pdf entrega el documento con Content-Disposition. Se descarga desde el panel del administrador, desde el del empleado y desde el del propio cliente, que solo puede bajar las suyas.</t>
@@ -2448,11 +2412,7 @@
           <t>Cumplido</t>
         </is>
       </c>
-      <c r="F24" s="19" t="inlineStr">
-        <is>
-          <t>[Pegar Captura de Pantalla Aquí]</t>
-        </is>
-      </c>
+      <c r="F24" s="19" t="n"/>
       <c r="G24" s="47" t="inlineStr">
         <is>
           <t>Tarjetas tipo Card con usuarios, catalogo, ventas del periodo, facturacion, ventas de hoy, acumulado del mes, valor del inventario y PQR recibidas con las que siguen sin cerrar.</t>
@@ -2485,11 +2445,7 @@
           <t>Cumplido</t>
         </is>
       </c>
-      <c r="F25" s="19" t="inlineStr">
-        <is>
-          <t>[Pegar Captura de Pantalla Aquí]</t>
-        </is>
-      </c>
+      <c r="F25" s="19" t="n"/>
       <c r="G25" s="46" t="inlineStr">
         <is>
           <t>Grafico de barras y grafico lineal sobre la misma serie, mas los Cards de indicadores y los repartos por estado y forma de pago. Se puede agrupar por dia, semana o mes. Estan dibujados en SVG propio, sin sumar ninguna libreria al proyecto.</t>
@@ -2522,11 +2478,7 @@
           <t>Cumplido</t>
         </is>
       </c>
-      <c r="F26" s="19" t="inlineStr">
-        <is>
-          <t>[Pegar Captura de Pantalla Aquí]</t>
-        </is>
-      </c>
+      <c r="F26" s="19" t="n"/>
       <c r="G26" s="47" t="inlineStr">
         <is>
           <t>Administrador, Empleado y Cliente llaman al mismo endpoint y reciben respuestas distintas. El empleado no ve el conteo de usuarios y el cliente solo ve sus propias cifras: el inventario y los totales del negocio le llegan en null.</t>
@@ -2559,11 +2511,7 @@
           <t>Cumplido</t>
         </is>
       </c>
-      <c r="F27" s="19" t="inlineStr">
-        <is>
-          <t>[Pegar Captura de Pantalla Aquí]</t>
-        </is>
-      </c>
+      <c r="F27" s="19" t="n"/>
       <c r="G27" s="46" t="inlineStr">
         <is>
           <t>Fecha inicial y final, agrupacion, estado, forma de pago, articulo y cliente. En la captura estan aplicados agrupacion por semana y estado Pagadas: el indicador baja de 60 a 50 ventas y el grafico pasa a barras semanales.</t>
@@ -2596,11 +2544,7 @@
           <t>Cumplido</t>
         </is>
       </c>
-      <c r="F28" s="19" t="inlineStr">
-        <is>
-          <t>[Pegar Captura de Pantalla Aquí]</t>
-        </is>
-      </c>
+      <c r="F28" s="19" t="n"/>
       <c r="G28" s="47" t="inlineStr">
         <is>
           <t>21 endpoints nuevos (45 en total) repartidos en ventas, facturas, reportes, PQR, estadisticas y chatbot, documentados en Swagger con sus codigos de respuesta.</t>
@@ -2633,11 +2577,7 @@
           <t>Cumplido</t>
         </is>
       </c>
-      <c r="F29" s="19" t="inlineStr">
-        <is>
-          <t>[Pegar Captura de Pantalla Aquí]</t>
-        </is>
-      </c>
+      <c r="F29" s="19" t="n"/>
       <c r="G29" s="46" t="inlineStr">
         <is>
           <t>Ninguna cifra esta escrita a mano en React: todo viene de GET /api/estadisticas/resumen y /api/estadisticas/ventas. La captura muestra los tres tokens contra el mismo endpoint y las respuestas distintas que devuelve.</t>
@@ -2670,11 +2610,7 @@
           <t>Cumplido</t>
         </is>
       </c>
-      <c r="F30" s="19" t="inlineStr">
-        <is>
-          <t>[Pegar Captura de Pantalla Aquí]</t>
-        </is>
-      </c>
+      <c r="F30" s="19" t="n"/>
       <c r="G30" s="47" t="inlineStr">
         <is>
           <t>El cliente radica peticion, queja, reclamo o sugerencia y recibe un numero de radicado (PQR-2026-000001). Cuatro estados: pendiente, en proceso, respondida y cerrada. El equipo responde y queda registrado quien atendio y cuando.</t>
@@ -2707,11 +2643,7 @@
           <t>Cumplido</t>
         </is>
       </c>
-      <c r="F31" s="19" t="inlineStr">
-        <is>
-          <t>[Pegar Captura de Pantalla Aquí]</t>
-        </is>
-      </c>
+      <c r="F31" s="19" t="n"/>
       <c r="G31" s="46" t="inlineStr">
         <is>
           <t>Chatbot flotante en todo el sitio publico. Atiende tambien a visitantes sin cuenta, responde con el catalogo real de la base de datos, orienta el proceso de compra y encauza las PQR. Las conversaciones quedan guardadas en las tablas conversaciones y mensajes.</t>
@@ -2744,11 +2676,7 @@
           <t>En Proceso</t>
         </is>
       </c>
-      <c r="F32" s="19" t="inlineStr">
-        <is>
-          <t>[Pegar Captura de Pantalla Aquí]</t>
-        </is>
-      </c>
+      <c r="F32" s="19" t="n"/>
       <c r="G32" s="47" t="inlineStr">
         <is>
           <t>La integracion esta construida y probada: FastAPI llama al proveedor (Anthropic u OpenAI, y cualquier API compatible cambiando IA_URL_BASE), le entrega el catalogo real como contexto y guarda el modelo que respondio en cada mensaje. Hay pruebas automaticas con el proveedor simulado. FALTA unicamente cargar una API Key en IA_API_KEY: sin ella el chatbot responde con su motor de reglas, que consulta la misma base de datos.</t>
@@ -2781,11 +2709,7 @@
           <t>Cumplido</t>
         </is>
       </c>
-      <c r="F33" s="19" t="inlineStr">
-        <is>
-          <t>[Pegar Captura de Pantalla Aquí]</t>
-        </is>
-      </c>
+      <c r="F33" s="19" t="n"/>
       <c r="G33" s="46" t="inlineStr">
         <is>
           <t>IA_API_KEY se lee de variables de entorno mediante pydantic-settings. El archivo .env esta en .gitignore y no hay ninguno versionado: en el repositorio solo viajan los .env.example sin valores. GET /api/chatbot/estado informa si hay clave configurada pero nunca la devuelve, y los errores del proveedor se registran sin el cuerpo de la peticion.</t>
@@ -2818,11 +2742,7 @@
           <t>En Proceso</t>
         </is>
       </c>
-      <c r="F34" s="19" t="inlineStr">
-        <is>
-          <t>[Pegar Captura de Pantalla Aquí]</t>
-        </is>
-      </c>
+      <c r="F34" s="19" t="n"/>
       <c r="G34" s="47" t="inlineStr">
         <is>
           <t>La configuracion esta lista y ensayada en local: railway.json y Procfile de cada servicio, Dockerfile como alternativa, servidor.js que resuelve las rutas de React Router en produccion, DATABASE_URL de la plataforma convertida al driver de SQLAlchemy y CORS por variable de entorno. Se probo el Frontend compilado contra el Backend en ENTORNO=produccion: enlaces directos sin 404 y preflight CORS correcto. FALTA ejecutar el despliegue y publicar la URL, que requiere crear las cuentas. Paso a paso en DESPLIEGUE.md.</t>
@@ -2855,14 +2775,10 @@
           <t>Cumplido</t>
         </is>
       </c>
-      <c r="F35" s="19" t="inlineStr">
-        <is>
-          <t>[Pegar Captura de Pantalla Aquí]</t>
-        </is>
-      </c>
+      <c r="F35" s="19" t="n"/>
       <c r="G35" s="46" t="inlineStr">
         <is>
-          <t>La base pasa de 7 a 13 tablas. Se agregan ventas, detalle_ventas, facturas, pqr, conversaciones y mensajes, con sus claves foraneas declaradas en la propia base. database/quinto_avance.sql es aditivo, para no perder los datos de los avances anteriores.</t>
+          <t>La base pasa de 7 a 14 tablas. Se agregan las siete entidades del criterio: ventas, detalle_ventas, facturas, detalle_facturas, pqr, conversaciones y mensajes, con sus claves foraneas declaradas en la propia base, no solo en el ORM. detalle_facturas guarda copia de las lineas al emitir: junto con los datos del cliente y los totales que ya copiaba la factura, el documento deja de depender de la venta. database/quinto_avance.sql es aditivo, para no perder los datos de avances anteriores.</t>
         </is>
       </c>
     </row>
@@ -2892,11 +2808,7 @@
           <t>Cumplido</t>
         </is>
       </c>
-      <c r="F36" s="19" t="inlineStr">
-        <is>
-          <t>[Pegar Captura de Pantalla Aquí]</t>
-        </is>
-      </c>
+      <c r="F36" s="19" t="n"/>
       <c r="G36" s="47" t="inlineStr">
         <is>
           <t>Se mantiene la separacion entre modelos ORM (SQLAlchemy, describen la tabla) y esquemas Pydantic (validan lo que entra y dan forma a lo que sale). Cinco modelos nuevos y seis archivos de esquemas para ventas, facturas, PQR, chat, reportes y estadisticas.</t>
@@ -2929,11 +2841,7 @@
           <t>Cumplido</t>
         </is>
       </c>
-      <c r="F37" s="19" t="inlineStr">
-        <is>
-          <t>[Pegar Captura de Pantalla Aquí]</t>
-        </is>
-      </c>
+      <c r="F37" s="19" t="n"/>
       <c r="G37" s="46" t="inlineStr">
         <is>
           <t>Los tres paneles se arman con los mismos componentes: MarcoPanel, Dashboard, TablaVentas, TablaFacturas, PanelPqr, PanelReportes, los graficos y las tarjetas. Cambia la lista de secciones que recibe cada rol, no el codigo. Todo conserva el sistema de diseno de los avances anteriores.</t>
@@ -2966,18 +2874,14 @@
           <t>Cumplido</t>
         </is>
       </c>
-      <c r="F38" s="19" t="inlineStr">
-        <is>
-          <t>[Pegar Captura de Pantalla Aquí]</t>
-        </is>
-      </c>
+      <c r="F38" s="19" t="n"/>
       <c r="G38" s="47" t="inlineStr">
         <is>
           <t>El mismo endpoint responde 401 sin token, 403 con token de rol insuficiente o invalido, y 200 con el correcto. Contrasenas con hash bcrypt de 12 rondas, credenciales en variables de entorno y topes en los endpoints publicos: 3 enlaces de recuperacion por correo cada 15 minutos y 25 mensajes de chatbot por equipo cada 10 minutos.</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="281.96" customHeight="1" s="43">
+    <row r="39" ht="327.56" customHeight="1" s="43">
       <c r="A39" s="24" t="inlineStr">
         <is>
           <t>REQ-25</t>
@@ -3003,14 +2907,10 @@
           <t>Cumplido</t>
         </is>
       </c>
-      <c r="F39" s="19" t="inlineStr">
-        <is>
-          <t>[Pegar Captura de Pantalla Aquí]</t>
-        </is>
-      </c>
+      <c r="F39" s="19" t="n"/>
       <c r="G39" s="46" t="inlineStr">
         <is>
-          <t>Coleccion de Postman con 84 peticiones en 12 carpetas (backend/postman/). Ademas, scripts/verificar_quinto_avance.py recorre la API contra MySQL real comprobando tanto lo que debe funcionar como lo que debe ser rechazado, y deja anuladas las ventas que crea. Se suman 130 pruebas automaticas con pytest.</t>
+          <t>Coleccion de Postman con 86 peticiones en 13 carpetas, ejecutada con newman (la CLI oficial de Postman): 97 aserciones, 0 fallos. Ejercita los cinco metodos: GET 45, POST 26, PATCH 8, DELETE 4 y PUT 3. La coleccion resuelve sola los identificadores contra el catalogo y genera datos unicos en cada ejecucion, asi que se puede repetir sin chocar consigo misma. Se suman 133 pruebas automaticas con pytest y el recorrido de scripts/verificar_quinto_avance.py contra MySQL real.</t>
         </is>
       </c>
     </row>

--- a/evidencias/quinto_avance/Lista_Chequeo_Quinto_Avance_DILIGENCIADA.xlsx
+++ b/evidencias/quinto_avance/Lista_Chequeo_Quinto_Avance_DILIGENCIADA.xlsx
@@ -1277,7 +1277,7 @@
       <row>31</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5191125" cy="3829050"/>
+    <ext cx="5191125" cy="5286375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="19" name="Image 19" descr="Picture"/>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="305.52" customHeight="1" s="43">
+    <row r="32" ht="421.8" customHeight="1" s="43">
       <c r="A32" s="25" t="inlineStr">
         <is>
           <t>REQ-18</t>
@@ -2673,13 +2673,13 @@
       </c>
       <c r="E32" s="18" t="inlineStr">
         <is>
-          <t>En Proceso</t>
+          <t>Cumplido</t>
         </is>
       </c>
       <c r="F32" s="19" t="n"/>
       <c r="G32" s="47" t="inlineStr">
         <is>
-          <t>La integracion esta construida y probada: FastAPI llama al proveedor (Anthropic u OpenAI, y cualquier API compatible cambiando IA_URL_BASE), le entrega el catalogo real como contexto y guarda el modelo que respondio en cada mensaje. Hay pruebas automaticas con el proveedor simulado. FALTA unicamente cargar una API Key en IA_API_KEY: sin ella el chatbot responde con su motor de reglas, que consulta la misma base de datos.</t>
+          <t>El chatbot responde con Inteligencia Artificial: FastAPI llama al proveedor desde el servidor, le entrega el catalogo real como contexto y guarda en cada mensaje el modelo que respondio. Funcionando con openai/gpt-oss-120b a traves de Groq, que expone una API compatible con la de OpenAI; basta cambiar IA_URL_BASE para usar Anthropic, OpenAI u otro proveedor. La captura muestra una conversacion real donde el modelo cita precios y unidades tomados de la base MySQL, no inventados. Si falta la clave el chatbot no se cae: vuelve solo a su motor de reglas, que consulta esa misma base.</t>
         </is>
       </c>
     </row>

--- a/evidencias/quinto_avance/Lista_Chequeo_Quinto_Avance_DILIGENCIADA.xlsx
+++ b/evidencias/quinto_avance/Lista_Chequeo_Quinto_Avance_DILIGENCIADA.xlsx
@@ -1327,7 +1327,7 @@
       <row>33</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5191125" cy="3248025"/>
+    <ext cx="5191125" cy="5715000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="21" name="Image 21" descr="Picture"/>
@@ -2716,7 +2716,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="259.16" customHeight="1" s="43">
+    <row r="34" ht="456" customHeight="1" s="43">
       <c r="A34" s="25" t="inlineStr">
         <is>
           <t>REQ-20</t>
@@ -2739,13 +2739,13 @@
       </c>
       <c r="E34" s="18" t="inlineStr">
         <is>
-          <t>En Proceso</t>
+          <t>Cumplido</t>
         </is>
       </c>
       <c r="F34" s="19" t="n"/>
       <c r="G34" s="47" t="inlineStr">
         <is>
-          <t>La configuracion esta lista y ensayada en local: railway.json y Procfile de cada servicio, Dockerfile como alternativa, servidor.js que resuelve las rutas de React Router en produccion, DATABASE_URL de la plataforma convertida al driver de SQLAlchemy y CORS por variable de entorno. Se probo el Frontend compilado contra el Backend en ENTORNO=produccion: enlaces directos sin 404 y preflight CORS correcto. FALTA ejecutar el despliegue y publicar la URL, que requiere crear las cuentas. Paso a paso en DESPLIEGUE.md.</t>
+          <t>Aplicacion desplegada y en funcionamiento. Frontend en Vercel: https://motoshub-react-fastapi.vercel.app ; Backend en Render: https://motoshub-react-fastapi.onrender.com ; base de datos MySQL en Aiven, con las 14 tablas y el historial de demostracion. Verificado en produccion: /salud responde "base_datos": "conectada", el entorno es "produccion", el catalogo sirve las 12 motocicletas, el login entrega token, los Dashboards traen indicadores, los reportes bajan en PDF y en Excel, el chatbot responde con IA y el preflight CORS autoriza el dominio del Frontend. Paso a paso reproducible en DESPLIEGUE.md.</t>
         </is>
       </c>
     </row>
